--- a/dataset_t6_grouped/results2/G4/G4_T3269_W0023F0002T0006Z000C1N112_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T3269_W0023F0002T0006Z000C1N112_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>71.58697119200144</v>
+        <v>11.63288281870024</v>
       </c>
       <c r="D2" t="n">
-        <v>78.01116868234155</v>
+        <v>12.6768149108805</v>
       </c>
       <c r="E2" t="n">
-        <v>6.165937067303656</v>
+        <v>1.001964773436844</v>
       </c>
       <c r="F2" t="n">
-        <v>10.40046910774937</v>
+        <v>1.690076230009273</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>72.94479898007705</v>
+        <v>11.85352983426252</v>
       </c>
       <c r="D3" t="n">
-        <v>71.91118905477144</v>
+        <v>11.68556822140036</v>
       </c>
       <c r="E3" t="n">
-        <v>6.165937067303656</v>
+        <v>1.001964773436844</v>
       </c>
       <c r="F3" t="n">
-        <v>10.40046910774937</v>
+        <v>1.690076230009273</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>68.60018350921834</v>
+        <v>11.14752982024798</v>
       </c>
       <c r="D4" t="n">
-        <v>67.07861621668867</v>
+        <v>10.90027513521191</v>
       </c>
       <c r="E4" t="n">
-        <v>6.165937067303656</v>
+        <v>1.001964773436844</v>
       </c>
       <c r="F4" t="n">
-        <v>10.40046910774937</v>
+        <v>1.690076230009273</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>56.02479609760108</v>
+        <v>9.104029365860177</v>
       </c>
       <c r="D5" t="n">
-        <v>47.3297773478825</v>
+        <v>7.691088819030906</v>
       </c>
       <c r="E5" t="n">
-        <v>6.165937067303656</v>
+        <v>1.001964773436844</v>
       </c>
       <c r="F5" t="n">
-        <v>10.40046910774937</v>
+        <v>1.690076230009273</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>71.00264094354269</v>
+        <v>11.53792915332569</v>
       </c>
       <c r="D6" t="n">
-        <v>69.94357849867886</v>
+        <v>11.36583150603532</v>
       </c>
       <c r="E6" t="n">
-        <v>6.165937067303656</v>
+        <v>1.001964773436844</v>
       </c>
       <c r="F6" t="n">
-        <v>10.40046910774937</v>
+        <v>1.690076230009273</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
